--- a/AAII_Financials/Quarterly/UMC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UMC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>UMC</t>
   </si>
@@ -656,540 +656,553 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2160400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1908600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1968300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1939600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2009200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1738900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1842200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1904400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1748400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1708700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1793800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1773400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1806200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1777000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2123900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2337900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2283400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1988300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1855700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1819800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1650900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1501500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1499300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1502300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1562800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1522500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1493200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1353300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1259300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1143000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1245900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1313500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1292200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1247200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1187200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1221800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1216600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1220200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1249200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1244500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1458700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1351500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1364600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1361500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1432100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1274600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1282600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1261200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1133300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1180100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1212600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1137600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1156400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1146800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1212100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1232000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1222700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1126000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1130300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1151100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1135000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1103100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1140200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1175200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1201700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1229900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1244500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1122600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1061800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1063700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1084500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1082700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1070200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1092800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>983100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1008100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>998200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>978000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>963500</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>973800</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>701600</v>
+      </c>
+      <c r="E10" s="3">
         <v>557200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>603700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>578100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>577100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>464200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>559600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>643200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>615100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>528600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>581200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>635800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>649800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>630200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>911900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1105900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1060700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>862300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>725400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>668700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>515900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>398300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>359100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>327100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>361200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>292600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>248600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>230700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>197500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>79400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>161400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>230800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>222000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>154400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>204100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>213700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>218400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>242200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>285600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>270700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1232,130 +1245,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>149200</v>
+      </c>
+      <c r="E12" s="3">
         <v>143100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>157200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>151900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>143400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>119100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>132200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>126600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>118600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>106600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>128700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>101200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>106400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>90700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>106700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>102500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>101700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>95100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>107200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>107500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>102700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>97200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>105700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>111000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>112800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>114700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>123200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>100900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>97400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>98500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>131400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>111000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>100700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>97300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>100100</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>108400</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>105200</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>130100</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>124700</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1476,52 +1493,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-66800</v>
+        <v>-800</v>
       </c>
       <c r="E14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3">
-        <v>16400</v>
-      </c>
       <c r="I14" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J14" s="3">
         <v>-500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-17900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-25700</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>91</v>
@@ -1532,23 +1552,23 @@
       <c r="T14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>91</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>91</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>91</v>
@@ -1556,24 +1576,24 @@
       <c r="AB14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>1600</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
@@ -1581,70 +1601,73 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>8200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>9700</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>3400</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>9400</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>34900</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>491100</v>
+      </c>
+      <c r="E15" s="3">
         <v>480600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>477600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>471900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>475500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>406600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>391700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>381500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>324700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>322400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>329900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>289700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>299300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>304600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1720,8 +1743,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1761,252 +1787,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1691300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1556400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1579400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1577000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1639400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1445400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1477800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1461100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1321000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1344900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1390000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1300100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1305700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1304300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1383900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1402700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1390900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1288100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1302600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1327100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1284100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1258500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1313500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1263500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1357000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1399500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1416000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1263300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1197700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1199000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1268200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1232300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1186400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1221600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1133800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1178700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1165900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1184800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1209800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1198300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>469100</v>
+      </c>
+      <c r="E18" s="3">
         <v>352300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>389000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>362600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>369800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>293500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>364300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>443300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>427500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>363800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>403800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>473300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>500500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>472700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>740100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>935200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>892500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>700200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>553200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>492600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>366900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>243000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>185900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>238800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>205800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>123000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>77200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>90000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>61500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-56000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-22300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>81200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>105800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>25600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>53400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>43100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>50700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>35400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>39300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>46200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2049,618 +2082,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-98600</v>
+        <v>-943500</v>
       </c>
       <c r="E20" s="3">
+        <v>-165100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-99400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-112800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>33300</v>
       </c>
-      <c r="H20" s="3">
-        <v>2800</v>
-      </c>
       <c r="I20" s="3">
+        <v>19800</v>
+      </c>
+      <c r="J20" s="3">
         <v>52900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-67400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-62800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-25300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-45300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-69200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-58900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-98800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>40900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>81200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-67800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>56600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>33100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>157400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>76000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>119500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>199400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>84800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>47200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-71100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>54100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>68700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-44200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-12800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>58400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>25000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>70200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>36700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>16600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>11300</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>931500</v>
+        <v>1903700</v>
       </c>
       <c r="E21" s="3">
+        <v>998000</v>
+      </c>
+      <c r="F21" s="3">
         <v>966000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>947300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>812000</v>
       </c>
-      <c r="H21" s="3">
-        <v>697200</v>
-      </c>
       <c r="I21" s="3">
+        <v>680300</v>
+      </c>
+      <c r="J21" s="3">
         <v>703200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>892100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>815000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>711400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>779000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>832100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>858600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>876200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1109000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1363500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1176800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1113800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>957300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1032600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>821400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>739800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>782200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>731000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>684300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>502000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>587100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>529800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>492400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>446900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>369000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>483500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>537800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>526000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>507000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>550400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>511800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>485400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>486800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>496600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E22" s="3">
         <v>11100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>10100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>14200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>15400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>15600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>15000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>18400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>22300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>26800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>26600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>23300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>23600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>22300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>21700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>20400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>18800</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>17200</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>15800</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1420300</v>
+      </c>
+      <c r="E23" s="3">
         <v>520400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>493700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>480400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>347200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>280900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>320800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>521500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>505500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>397900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>478200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>579500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>593100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>627000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>767900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1003000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>810600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>741400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>570700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>633200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>427900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>350100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>371800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>308200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>234600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>29600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>105800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>70900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>40000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-12300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-90700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>27600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>69400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>61800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>56700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>92900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>68600</v>
-      </c>
-      <c r="AN23" s="3">
-        <v>34800</v>
       </c>
       <c r="AO23" s="3">
         <v>34800</v>
       </c>
       <c r="AP23" s="3">
+        <v>34800</v>
+      </c>
+      <c r="AQ23" s="3">
         <v>63600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>93100</v>
+      </c>
+      <c r="E24" s="3">
         <v>16500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>175300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>44700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>48200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>62700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>66800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>81400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>71700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>47600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>83400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>83100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>89900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>169300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>155200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>129500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>112300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>68100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>68400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>43100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>34900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-15500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>14500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>21100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-11000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-39000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>18000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>13000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>20700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-14000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>20100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2781,252 +2830,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1327200</v>
+      </c>
+      <c r="E26" s="3">
         <v>504000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>318400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>490200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>302600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>232700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>258100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>454700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>424000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>326200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>430600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>496100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>510000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>537100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>598600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>847900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>681000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>629100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>502500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>564800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>384800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>315300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>360400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>301600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>213100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>44300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>112600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>69500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>32900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-105200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>80400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>100800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>38700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>79900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>47900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>48800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>14600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1328300</v>
+      </c>
+      <c r="E27" s="3">
         <v>505700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>320200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>491500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>304400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>233700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>259200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>455700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>424400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>327000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>430700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>496300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>501800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>530500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>597000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>837200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>675800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>621000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>568300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>387300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>332400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>370600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>304900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>235200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>79500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>136900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>105000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>60800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>42100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-59900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>57400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>121700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>113100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>57400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>112500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>68000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>74500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>83100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>97000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3147,8 +3205,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3269,8 +3330,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3391,8 +3455,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3513,252 +3580,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>98600</v>
+        <v>943500</v>
       </c>
       <c r="E32" s="3">
+        <v>165100</v>
+      </c>
+      <c r="F32" s="3">
         <v>99400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>112800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-33300</v>
       </c>
-      <c r="H32" s="3">
-        <v>-2800</v>
-      </c>
       <c r="I32" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="J32" s="3">
         <v>-52900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>67400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>62800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>25300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>45300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>69200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>58900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>98800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-40900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-81200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>67800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-56600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-33100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-157400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-76000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-119500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-199400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-84800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-47200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>71100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-54100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-68700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>44200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>30300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>12800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-58400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-70200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-36700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-16600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-11300</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-29700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1328300</v>
+      </c>
+      <c r="E33" s="3">
         <v>505700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>320200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>491500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>304400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>233700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>259200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>455700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>424400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>327000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>430700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>496300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>501800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>530500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>597000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>837200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>675800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>621000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>500800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>568300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>387300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>332400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>370600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>304900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>235200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>79500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>136900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>105000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>60800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>42100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-59900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>57400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>121700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>113100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>57400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>112500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>68000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>74500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>83100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>97000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3879,257 +3955,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1328300</v>
+      </c>
+      <c r="E35" s="3">
         <v>505700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>320200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>491500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>304400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>233700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>259200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>455700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>424400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>327000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>430700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>496300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>501800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>530500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>597000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>837200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>675800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>621000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>500800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>568300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>387300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>332400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>370600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>304900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>235200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>79500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>136900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>105000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>60800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>42100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-59900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>57400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>121700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>113100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>57400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>112500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>68000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>74500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>83100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>97000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4172,8 +4257,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4216,1106 +4302,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3919700</v>
+      </c>
+      <c r="E41" s="3">
         <v>3409000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3524000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3418800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3829600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3196300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3203200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3255800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3731900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3735400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4326400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4370500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5232700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5632800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5442300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5601900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5822200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5397500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4164300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3681600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4021300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3420300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3113000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3309100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3516500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3427900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3407200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3111000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3157900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3112900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2934900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2718700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2500900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2565800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2647100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2266700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2208200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1983100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1877700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1802200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E42" s="3">
         <v>789400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>563800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>486200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>398500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>316000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>312300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>346900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>292800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>399300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>402400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>161900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>164700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>177200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>149700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>124600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>214400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>215600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>296600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>240600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>33100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>32900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>40300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>30700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>35700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>27100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>25800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>22700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>21400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>19400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>18500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>14100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>15600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>17400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>23200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>27400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>25900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>28300</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>23300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1287300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1222500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1098800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1136200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1174400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1114200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1089200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1148600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1085800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1096800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1082400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1054700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1074800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>960600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1227200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1453100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1407400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1228100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1142000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1119000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1025500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>988700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>967800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>940100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1000100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1084200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>949900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>871600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>898200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>832500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>866400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>908900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>959500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>886600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>734300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>785600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>748200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>705300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>782700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>761800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1191800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1208400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1185500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1154100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1163300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1064600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1091600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1199300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1118400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1082000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1165600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1136100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1108600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1071200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>972800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>933500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>866400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>796300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>722600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>753500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>727700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>708500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>746500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>765500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>821900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>797000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>774800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>716800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>686000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>662100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>638600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>586600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>587300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>570000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>591700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>554300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>527800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>530300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>554300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>559800</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E45" s="3">
         <v>45700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>26600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>49100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>23000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>25600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>109700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>164900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>112100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>190000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>999200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1093000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>932400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>558800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>571000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>427800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>539500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>412500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>328400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1140600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>496600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>522700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>494800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>445900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>496100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>497500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>513800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>407900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>381500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>390200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>364400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>340000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>7237500</v>
+      </c>
+      <c r="E46" s="3">
         <v>6768000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6521300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6326400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6674000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5780000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5786400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6095800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6378600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6416700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7076100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6814200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7668900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7931800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7901700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8278000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8422500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7827600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7324800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6887700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6740000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5709200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5438500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5473200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5913700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5748600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5486100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5862800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5260200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5149600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4953100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4674100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4559400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4537400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4510200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4041800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3891700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3637200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3602400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>3488300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>4615700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2714600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2400200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2370600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2358500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2146000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2211300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2414400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2413400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2425200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2423600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2202900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2260400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2363000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2030600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1920600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2103400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2269500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2278000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2044700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2158400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2067000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1872700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1571400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1476500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1291600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1475200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1446500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1322600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1305600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1175400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1209300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1241200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1199400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1102700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1125500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1163800</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1138100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1133700</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1232600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8382100</v>
+      </c>
+      <c r="E48" s="3">
         <v>8611600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8880700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8948400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9093100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8715500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8758300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8957600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8667700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8188000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8033300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6825500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6606100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6547100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6200400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5378700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4814400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4615900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4565300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4572700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4350600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4337400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4670700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4733300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4972200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5388900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5669000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5641600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5850300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6191600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6086700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5969600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6308800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6577800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>6677400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>6764100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>6921700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>7101400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>7375100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>7060600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>143600</v>
+      </c>
+      <c r="E49" s="3">
         <v>139500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>151000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>146200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>128600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>117500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>126700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>121300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>122500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>125800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>142700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>123800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>119100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>130200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>133900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>130300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>130500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>112900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>114500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>136400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>151100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>148500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>161500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>165800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>170400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>172000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>185500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>130600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>145100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>117600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>105000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>106900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>119100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>122700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>122800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>125500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>123900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>120300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>133300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>138400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5436,8 +5550,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5558,130 +5675,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>240500</v>
+      </c>
+      <c r="E52" s="3">
         <v>222800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>213500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>253800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>306700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>298500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>353000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>323700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>333000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>422900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>408600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>882200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>928800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>878900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>423200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>398900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>366500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>313300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>300500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>315700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>275000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>307100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>352400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>385100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>408300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>382600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>392600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>331700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>351000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>360400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>470300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>468600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>439900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>386500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>359800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>394100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>403200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>374500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>364200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>307400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5802,130 +5925,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>20932700</v>
+      </c>
+      <c r="E54" s="3">
         <v>18759600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18438200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18219200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18743800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17219500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17394800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18081700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18068200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17736000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18251400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17006600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17748300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18017100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16689900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16106400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15837200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15139200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14583000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13957200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13675000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12569100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12495800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12328800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12941200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12983600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13208300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13413200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12929200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13124700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12790300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12428500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12668400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12823700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12772800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>12451000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>12504300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>12371600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>12608800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>12227400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5968,8 +6097,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -6012,740 +6142,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>284600</v>
+      </c>
+      <c r="E57" s="3">
         <v>283700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>292000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>263700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>292000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>278700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>232900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>283700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>251900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>233300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>245600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>260100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>283300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>302000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>281200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>311300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>315300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>284100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>262600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>269000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>273100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>263400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>260200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>257800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>301300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>321400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>316700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>237700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>241600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>237800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>238600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>229600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>246400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>232700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>211800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>214200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>215400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>210000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>223500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>219900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>396300</v>
+      </c>
+      <c r="E58" s="3">
         <v>735300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>898700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1010000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>749300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>549100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>614600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>991300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>516800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>817700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>980800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>950800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>388900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>338200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>254400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>395400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>434900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>725600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1250200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>807600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>655200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1206200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1277400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>567500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>630000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>933900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1333700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1454100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1393900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>834900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>639300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>677900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>573100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1330300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1711600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1579800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1561900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1185000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1012600</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1534200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>2660400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1448800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1574000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1405300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2713000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1338600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1429500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1487700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3057400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1689600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1980700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1626700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3896400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2830800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2863600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2642600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3427000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1909600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1798500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1675300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1828400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1034000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1052200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1155100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1361200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>945700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>944000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>830100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1057600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>774100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>872500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>807700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1148500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>850600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>930700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>875200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1064900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>785700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1111100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>967000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>3341400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2489400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2789600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2699000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3774900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2190100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2295900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2779300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3847000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2764900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3231800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2861100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4587200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3471000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3399200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3349300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4177200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2919300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3311200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2752000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2756700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2503600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2589900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1980400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2292500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2201000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2594400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2521900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2693100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1846800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1750500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1715300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1968000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2413600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2854100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2669200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2842200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2180600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2347200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2721000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1598100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1642300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1616100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1942200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1606500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1512500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1870500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2015600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1624400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1528300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1635700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1690100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1318600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1392800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1411400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1594800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1617600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1710100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1392300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1813400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1807600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1040200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>986300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1829400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2073100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1906100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1903500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2169100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1775100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2473700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2353300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2249800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2253800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1749900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1728100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1696900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1660600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2032000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1980400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1294100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1288900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1287400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1297200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1324600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1361600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1293400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1302100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1313000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1302500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1310400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1330100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1288000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1066400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1214100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1376400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1388200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1066300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1033100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1049700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1006900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1321300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1065800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1115500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1122900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1209700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1282900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1316900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1369400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1397900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1444000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1441300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1374600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1435900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1469000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1253700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1135100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1091800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1092900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1148100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1070700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6866,8 +7015,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6988,8 +7140,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7110,130 +7265,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>6979400</v>
+      </c>
+      <c r="E66" s="3">
         <v>6041100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6341700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6370400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7218500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5473800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5857700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6479700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7106800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5906400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6515100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6129700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7260700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6362100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6197700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6344100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6872700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5671800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5760200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5577200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5889000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4612600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4695500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4937700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5577900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5392400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5829500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6074900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5881100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5780400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5561400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5356200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5678100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5639300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5866800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5535000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5624800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5336500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>5546200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>5138300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7276,8 +7437,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7398,8 +7560,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7520,8 +7685,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7642,8 +7810,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7764,130 +7935,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>8259200</v>
+      </c>
+      <c r="E72" s="3">
         <v>7788200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7416200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7305700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7103300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7051000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6920300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6869500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6270700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7115700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7084400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6324800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6056500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7151100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6332400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5685700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4954900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4233200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3622800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3263200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2671100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2880200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2653800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2342000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2144500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2400700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2181900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2072300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1935700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2153400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2160500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2158800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2129100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2307700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1557800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1529000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1457800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1603500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1554000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1561100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -8008,8 +8185,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8130,8 +8310,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8252,130 +8435,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>13953200</v>
+      </c>
+      <c r="E76" s="3">
         <v>12717300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12093800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11844300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11519300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11739000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11529200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11593000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10951800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11819700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11725200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10866300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10476600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11643800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10492200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9762300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8964500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9467400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8822800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8380000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7786000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7956500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7800300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7391100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7363400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7591300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7378800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7338400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7048200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7344400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7228900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7072400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6990300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7184400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6905900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6916000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6879500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7035100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7062700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>7089100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8496,257 +8685,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1328300</v>
+      </c>
+      <c r="E81" s="3">
         <v>505700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>320200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>491500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>304400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>233700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>259200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>455700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>424400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>327000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>430700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>496300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>501800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>530500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>597000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>837200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>675800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>621000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>500800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>568300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>387300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>332400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>370600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>304900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>235200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>79500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>136900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>105000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>60800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>42100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-59900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>57400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>121700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>113100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>57400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>112500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>68000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>74500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>83100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>97000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8789,130 +8987,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>471900</v>
+      </c>
+      <c r="E83" s="3">
         <v>403500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>386500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>379700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>322800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>320800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>324900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>288900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>297900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>302300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>318700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>330300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>348800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>372000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>328000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>347200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>352000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>357100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>371000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>382600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>378500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>377300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>397000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>407400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>431300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>450100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>455800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>432100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>425900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>434300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>435500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>432700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>444800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>442000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>428700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>437100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>424300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>433500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>436200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>420700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9033,8 +9235,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9155,8 +9360,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9277,8 +9485,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9399,8 +9610,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9521,130 +9735,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1059200</v>
+      </c>
+      <c r="E89" s="3">
         <v>687300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1051000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>686800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>755600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>716000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1006000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>546200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>699600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>651200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>855700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>592300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>441500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>883900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1282300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1231000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1112000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>944200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>842200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>720200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>749900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>582800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>532000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>620700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>577500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>530600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1339200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-110400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>428800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>287100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>425300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>526000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>474400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>291900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>418100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>371000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>480200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>434100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>507000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>452900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9687,130 +9907,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-277300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-391700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-472100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-368200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-257900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-425300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-557500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-684100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-616900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-891300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-663700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-535900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-774500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-975400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-36391900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-23546300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11722400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11223100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-14806900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-17827500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-276300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-234400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-388500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-224500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-150300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-130800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-124900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-127300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-136400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-195100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-153000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-187200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-129700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-190100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-355300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-236200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-270100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-588000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-724600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-666200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9931,8 +10155,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10053,130 +10280,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-233400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-667500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-543200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-529800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-322700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-315700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-517600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-753400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-465800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-935600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-875200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-550700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-759300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-969800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1128600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-664200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-371300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>462500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-418800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-755900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-599400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-227000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-577200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-190400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-277400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-328200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-636700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-142300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-146400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-199400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-161800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-182600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>22200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-195500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-161500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-262700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-531300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-597400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-502200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10219,8 +10452,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -10230,23 +10464,23 @@
       <c r="E96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G96" s="3">
         <v>1174000</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>1183400</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>91</v>
@@ -10254,21 +10488,21 @@
       <c r="M96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O96" s="3">
         <v>1398900</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="P96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R96" s="3">
         <v>100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -10300,11 +10534,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>100</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -10324,11 +10558,11 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>300</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
@@ -10339,10 +10573,13 @@
         <v>0</v>
       </c>
       <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-225200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10463,8 +10700,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10585,8 +10825,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10707,370 +10950,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-338000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-115300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-363500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-497300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>39300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-414000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-436400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-401400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-175600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-201400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-127000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-857700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>34000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>44200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-287600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-827600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-425300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-249500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>199900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-315500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>429300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>82200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-104300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-457100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-103800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-210700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-346700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>148300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-226000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>76500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-200800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-108500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-359000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-456100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>169000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-149200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>22900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>255800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>137600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>289700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-279300</v>
+      </c>
+      <c r="E101" s="3">
         <v>54400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>33800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>10500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>75400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-117500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>118400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-23300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-83200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>167900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>53800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>92100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-80000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>165500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>50700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>82700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-10400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-37800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-44200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-24800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>13900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>12500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-23900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-11100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-53200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>28300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-49900</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>493100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-51300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>205200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-255100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>192900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>48600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-574800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>68700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-410400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-264000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-697800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-280300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-213900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-95300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>366100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1239800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>612800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-354700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>542100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>422000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-158600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-34600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>165700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>311700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-129200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>56700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>178100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>75100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>211000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-64900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-150700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>380400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>58500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>237300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>105400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>75400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>190500</v>
       </c>
     </row>
